--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D5ED6C-D6F7-4F5D-8F34-03D6E40CE926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C16AB12-4FF7-4E14-90B0-5E0EED130CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21165" yWindow="4125" windowWidth="28725" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14790" yWindow="4845" windowWidth="28725" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -198,17 +198,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -695,7 +698,7 @@
         <v>300</v>
       </c>
       <c r="E4" s="5">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5">
         <v>10</v>
@@ -707,7 +710,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>100</v>
@@ -733,7 +736,7 @@
         <v>1500</v>
       </c>
       <c r="E5" s="5">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5">
         <v>20</v>
@@ -745,7 +748,7 @@
         <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
         <v>500</v>
@@ -771,7 +774,7 @@
         <v>2000</v>
       </c>
       <c r="E6" s="5">
-        <v>700</v>
+        <v>7</v>
       </c>
       <c r="F6" s="5">
         <v>50</v>
@@ -783,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J6" s="5">
         <v>800</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C16AB12-4FF7-4E14-90B0-5E0EED130CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E449C6-67FB-4660-8579-32FCB12C66A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14790" yWindow="4845" windowWidth="28725" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21645" yWindow="4935" windowWidth="28725" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
+    <sheet name="ConfProjectile" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
   <si>
     <t>ID</t>
   </si>
@@ -178,6 +179,85 @@
   </si>
   <si>
     <t>GrizzlyTank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹类型
+1=子弹；
+2=炮弹；</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞行速度</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsHoming</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>追踪类型导弹</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>炮弹</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>步枪子弹</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>机枪子弹</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shell</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cartridge</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹类型
+（指向ConfProjectile表）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -185,7 +265,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,16 +310,28 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -262,13 +354,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -285,6 +388,36 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -554,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -562,15 +695,16 @@
     <col min="4" max="4" width="6.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.25" customWidth="1"/>
     <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="44.625" customWidth="1"/>
+    <col min="7" max="7" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,32 +717,35 @@
       <c r="D1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -621,13 +758,13 @@
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -639,14 +776,17 @@
       <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -659,32 +799,35 @@
       <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="14" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -697,32 +840,35 @@
       <c r="D4" s="5">
         <v>300</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="15">
         <v>1</v>
       </c>
       <c r="F4" s="5">
         <v>10</v>
       </c>
       <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
         <v>1000</v>
       </c>
-      <c r="H4" s="5">
+      <c r="I4" s="5">
         <v>1</v>
       </c>
-      <c r="I4" s="5">
+      <c r="J4" s="5">
         <v>2</v>
       </c>
-      <c r="J4" s="5">
+      <c r="K4" s="5">
         <v>100</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -735,32 +881,35 @@
       <c r="D5" s="5">
         <v>1500</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="15">
         <v>3</v>
       </c>
       <c r="F5" s="5">
         <v>20</v>
       </c>
       <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
         <v>200</v>
       </c>
-      <c r="H5" s="5">
+      <c r="I5" s="5">
         <v>8</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
         <v>500</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -773,28 +922,31 @@
       <c r="D6" s="5">
         <v>2000</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="15">
         <v>7</v>
       </c>
       <c r="F6" s="5">
         <v>50</v>
       </c>
       <c r="G6" s="5">
+        <v>3</v>
+      </c>
+      <c r="H6" s="5">
         <v>2000</v>
       </c>
-      <c r="H6" s="5">
+      <c r="I6" s="5">
         <v>1</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>2</v>
       </c>
-      <c r="J6" s="5">
+      <c r="K6" s="5">
         <v>800</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -803,4 +955,157 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DBC2DB-D077-4C22-AD9B-3F1912F98524}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="5" width="10.75" style="9" customWidth="1"/>
+    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.15">
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>30</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>70</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E449C6-67FB-4660-8579-32FCB12C66A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C07C877-0216-46CD-AE6B-7307591E6173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21645" yWindow="4935" windowWidth="28725" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7935" yWindow="2460" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
@@ -136,10 +136,6 @@
   </si>
   <si>
     <t>AtkInterval</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击频率</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -196,10 +192,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>飞行速度</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>IsHoming</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -208,32 +200,8 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Note</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>炮弹</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>伤害</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>步枪子弹</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>机枪子弹</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Shell</t>
@@ -258,6 +226,64 @@
   </si>
   <si>
     <t>ProjectileID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击范围</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击频率
+1000=1秒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞行速度
+（最大15）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>步枪子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>机枪子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>炮弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音频</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>badger_tank_200ms</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>grizzly_tank_1000ms</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>infantry_200ms</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AudioClip</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -331,7 +357,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -354,24 +380,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -397,15 +412,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -687,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -695,16 +701,17 @@
     <col min="4" max="4" width="6.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.25" customWidth="1"/>
     <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="44.625" customWidth="1"/>
+    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -717,35 +724,38 @@
       <c r="D1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -758,7 +768,7 @@
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="10" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -767,7 +777,7 @@
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -779,19 +789,22 @@
       <c r="K2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>7</v>
@@ -799,35 +812,38 @@
       <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="K3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -835,40 +851,43 @@
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="5">
         <v>300</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="12">
         <v>1</v>
       </c>
       <c r="F4" s="5">
         <v>10</v>
       </c>
       <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
         <v>1</v>
       </c>
-      <c r="H4" s="5">
-        <v>1000</v>
-      </c>
       <c r="I4" s="5">
+        <v>5000</v>
+      </c>
+      <c r="J4" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
       <c r="K4" s="5">
+        <v>5</v>
+      </c>
+      <c r="L4" s="5">
         <v>100</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="M4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -876,40 +895,43 @@
         <v>2</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="5">
         <v>1500</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="12">
         <v>3</v>
       </c>
       <c r="F5" s="5">
         <v>20</v>
       </c>
       <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
         <v>2</v>
       </c>
-      <c r="H5" s="5">
-        <v>200</v>
-      </c>
       <c r="I5" s="5">
+        <v>2000</v>
+      </c>
+      <c r="J5" s="5">
         <v>8</v>
       </c>
-      <c r="J5" s="5">
-        <v>2</v>
-      </c>
       <c r="K5" s="5">
+        <v>5</v>
+      </c>
+      <c r="L5" s="5">
         <v>500</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -917,36 +939,39 @@
         <v>3</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5">
         <v>2000</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="12">
         <v>7</v>
       </c>
       <c r="F6" s="5">
         <v>50</v>
       </c>
       <c r="G6" s="5">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5">
         <v>3</v>
       </c>
-      <c r="H6" s="5">
-        <v>2000</v>
-      </c>
       <c r="I6" s="5">
+        <v>20000</v>
+      </c>
+      <c r="J6" s="5">
         <v>1</v>
       </c>
-      <c r="J6" s="5">
-        <v>2</v>
-      </c>
       <c r="K6" s="5">
+        <v>5</v>
+      </c>
+      <c r="L6" s="5">
         <v>800</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="N6" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -959,14 +984,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DBC2DB-D077-4C22-AD9B-3F1912F98524}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="5" width="10.75" style="9" customWidth="1"/>
+    <col min="2" max="5" width="10.75" customWidth="1"/>
     <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -974,22 +1000,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>43</v>
+      <c r="G1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -997,45 +1026,51 @@
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>44</v>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="E3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>45</v>
+      <c r="G3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1043,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -1052,13 +1087,16 @@
         <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1066,7 +1104,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -1075,13 +1113,16 @@
         <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1089,7 +1130,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -1098,10 +1139,13 @@
         <v>70</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C07C877-0216-46CD-AE6B-7307591E6173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9FDB74-CDF9-40F4-9AD6-3D5A94EA240C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7935" yWindow="2460" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,11 +237,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>攻击频率
-1000=1秒</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>飞行速度
 （最大15）</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -284,6 +279,11 @@
   </si>
   <si>
     <t>AudioClip</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击频率
+10000=1秒</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -825,7 +825,7 @@
         <v>46</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>27</v>
@@ -1012,10 +1012,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
@@ -1052,7 +1052,7 @@
         <v>36</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>40</v>
@@ -1064,10 +1064,10 @@
         <v>7</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1090,10 +1090,10 @@
         <v>43</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1116,10 +1116,10 @@
         <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1142,10 +1142,10 @@
         <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9FDB74-CDF9-40F4-9AD6-3D5A94EA240C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035D8886-208E-4617-8EE2-5BBBC4393003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7935" yWindow="2460" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15195" yWindow="2850" windowWidth="34440" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -869,7 +869,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="J4" s="5">
         <v>1</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>43</v>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>44</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>42</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035D8886-208E-4617-8EE2-5BBBC4393003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39CE067-CA2B-450E-8281-A9B5FC9D8D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15195" yWindow="2850" windowWidth="34440" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13800" yWindow="3330" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -339,6 +339,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -898,7 +899,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="5">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="E5" s="12">
         <v>3</v>
@@ -942,7 +943,7 @@
         <v>35</v>
       </c>
       <c r="D6" s="5">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E6" s="12">
         <v>7</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39CE067-CA2B-450E-8281-A9B5FC9D8D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71EBBC9-6EEF-4D6B-8074-6134E202A658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13800" yWindow="3330" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="1965" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
   <si>
     <t>ID</t>
   </si>
@@ -284,6 +284,14 @@
   <si>
     <t>攻击频率
 10000=1秒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProduceTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产时间（毫秒）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -694,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -708,11 +716,12 @@
     <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="44.625" customWidth="1"/>
+    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -749,14 +758,17 @@
       <c r="L1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -794,13 +806,16 @@
         <v>8</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -837,14 +852,17 @@
       <c r="L3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -881,14 +899,17 @@
       <c r="L4" s="5">
         <v>100</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="5">
+        <v>1800</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="O4" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -925,14 +946,17 @@
       <c r="L5" s="5">
         <v>500</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="5">
+        <v>7000</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="O5" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -969,10 +993,13 @@
       <c r="L6" s="5">
         <v>800</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="5">
+        <v>7000</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="O6" s="5" t="s">
         <v>25</v>
       </c>
     </row>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71EBBC9-6EEF-4D6B-8074-6134E202A658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0F1CB2-77A9-48D6-B57B-D03E5B0A7E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="1965" windowWidth="34440" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17505" yWindow="3525" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -938,7 +938,7 @@
         <v>2000</v>
       </c>
       <c r="J5" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>5</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0F1CB2-77A9-48D6-B57B-D03E5B0A7E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906AA26D-EBAC-43D4-89AF-09C1ED66AE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17505" yWindow="3525" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20520" yWindow="4140" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
   <si>
     <t>ID</t>
   </si>
@@ -292,6 +292,26 @@
   </si>
   <si>
     <t>生产时间（毫秒）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/Infantry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/BadgerTank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/GrizzlyTank</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -702,26 +722,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
     <col min="3" max="3" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="44.625" customWidth="1"/>
+    <col min="4" max="4" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.25" customWidth="1"/>
+    <col min="7" max="7" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -731,44 +752,47 @@
       <c r="C1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -778,22 +802,22 @@
       <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="4" t="s">
@@ -805,17 +829,20 @@
       <c r="L2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -825,181 +852,193 @@
       <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="5">
         <v>300</v>
       </c>
-      <c r="E4" s="12">
+      <c r="F4" s="12">
         <v>1</v>
-      </c>
-      <c r="F4" s="5">
-        <v>10</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
         <v>1</v>
       </c>
-      <c r="I4" s="5">
+      <c r="J4" s="5">
         <v>2000</v>
       </c>
-      <c r="J4" s="5">
+      <c r="K4" s="5">
         <v>1</v>
       </c>
-      <c r="K4" s="5">
+      <c r="L4" s="5">
         <v>5</v>
       </c>
-      <c r="L4" s="5">
+      <c r="M4" s="5">
         <v>100</v>
       </c>
-      <c r="M4" s="5">
+      <c r="N4" s="5">
         <v>1800</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="O4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="5">
         <v>2400</v>
       </c>
-      <c r="E5" s="12">
+      <c r="F5" s="12">
         <v>3</v>
       </c>
-      <c r="F5" s="5">
+      <c r="G5" s="5">
         <v>20</v>
       </c>
-      <c r="G5" s="5">
+      <c r="H5" s="5">
         <v>10</v>
       </c>
-      <c r="H5" s="5">
+      <c r="I5" s="5">
         <v>2</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="5">
         <v>2000</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>5</v>
       </c>
       <c r="L5" s="5">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5">
         <v>500</v>
       </c>
-      <c r="M5" s="5">
+      <c r="N5" s="5">
         <v>7000</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="O5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="P5" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="5">
         <v>3000</v>
       </c>
-      <c r="E6" s="12">
+      <c r="F6" s="12">
         <v>7</v>
       </c>
-      <c r="F6" s="5">
+      <c r="G6" s="5">
         <v>50</v>
       </c>
-      <c r="G6" s="5">
+      <c r="H6" s="5">
         <v>15</v>
       </c>
-      <c r="H6" s="5">
+      <c r="I6" s="5">
         <v>3</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>20000</v>
       </c>
-      <c r="J6" s="5">
+      <c r="K6" s="5">
         <v>1</v>
       </c>
-      <c r="K6" s="5">
+      <c r="L6" s="5">
         <v>5</v>
       </c>
-      <c r="L6" s="5">
+      <c r="M6" s="5">
         <v>800</v>
       </c>
-      <c r="M6" s="5">
+      <c r="N6" s="5">
         <v>7000</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="O6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="P6" s="5" t="s">
         <v>25</v>
       </c>
     </row>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906AA26D-EBAC-43D4-89AF-09C1ED66AE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B6865C-CB1C-4912-A725-22B6F1D900EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20520" yWindow="4140" windowWidth="19995" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9360" yWindow="2160" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -312,6 +312,10 @@
   </si>
   <si>
     <t>images/GrizzlyTank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>碉堡机枪子弹</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -386,7 +390,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -409,13 +413,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -453,6 +468,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -761,7 +779,7 @@
       <c r="F1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="10" t="s">
         <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -811,7 +829,7 @@
       <c r="F2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="10" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -861,7 +879,7 @@
       <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="11" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="6" t="s">
@@ -911,7 +929,7 @@
       <c r="F4" s="12">
         <v>1</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="12">
         <v>10</v>
       </c>
       <c r="H4" s="5">
@@ -921,7 +939,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
@@ -961,7 +979,7 @@
       <c r="F5" s="12">
         <v>3</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="12">
         <v>20</v>
       </c>
       <c r="H5" s="5">
@@ -971,7 +989,7 @@
         <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="K5" s="5">
         <v>5</v>
@@ -1011,7 +1029,7 @@
       <c r="F6" s="12">
         <v>7</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="12">
         <v>50</v>
       </c>
       <c r="H6" s="5">
@@ -1051,12 +1069,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DBC2DB-D077-4C22-AD9B-3F1912F98524}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="5" width="10.75" customWidth="1"/>
     <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.25">
@@ -1151,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>43</v>
@@ -1177,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>44</v>
@@ -1213,6 +1232,32 @@
       </c>
       <c r="H6" s="2" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13">
+        <v>1</v>
+      </c>
+      <c r="C7" s="13">
+        <v>10</v>
+      </c>
+      <c r="D7" s="13">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B6865C-CB1C-4912-A725-22B6F1D900EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FACF40-6A1F-4692-95DA-71F78A858368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="2160" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -470,7 +470,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -945,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>100</v>
@@ -995,7 +995,7 @@
         <v>5</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5" s="5">
         <v>500</v>
@@ -1045,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" s="5">
         <v>800</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FACF40-6A1F-4692-95DA-71F78A858368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1CF48A-79A5-41AE-AE1D-AF6DBA1DCB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14790" yWindow="3780" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
   <si>
     <t>ID</t>
   </si>
@@ -316,6 +316,14 @@
   </si>
   <si>
     <t>碉堡机枪子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AutoHeal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动回血万分比</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -740,27 +748,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
     <col min="3" max="3" width="15.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="44.625" customWidth="1"/>
+    <col min="6" max="6" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.25" customWidth="1"/>
+    <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -776,41 +785,44 @@
       <c r="E1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -826,19 +838,19 @@
       <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="10" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -850,17 +862,20 @@
       <c r="M2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -876,41 +891,44 @@
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -926,41 +944,44 @@
       <c r="E4" s="5">
         <v>300</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="5">
+        <v>500</v>
+      </c>
+      <c r="G4" s="12">
         <v>1</v>
       </c>
-      <c r="G4" s="12">
+      <c r="H4" s="12">
         <v>10</v>
       </c>
-      <c r="H4" s="5">
+      <c r="I4" s="5">
         <v>10</v>
       </c>
-      <c r="I4" s="5">
+      <c r="J4" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="5">
+      <c r="K4" s="5">
         <v>4000</v>
       </c>
-      <c r="K4" s="5">
+      <c r="L4" s="5">
         <v>1</v>
       </c>
-      <c r="L4" s="5">
+      <c r="M4" s="5">
         <v>4</v>
       </c>
-      <c r="M4" s="5">
+      <c r="N4" s="5">
         <v>100</v>
       </c>
-      <c r="N4" s="5">
+      <c r="O4" s="5">
         <v>1800</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="Q4" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -976,41 +997,44 @@
       <c r="E5" s="5">
         <v>2400</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="5">
+        <v>200</v>
+      </c>
+      <c r="G5" s="12">
         <v>3</v>
       </c>
-      <c r="G5" s="12">
+      <c r="H5" s="12">
         <v>20</v>
       </c>
-      <c r="H5" s="5">
+      <c r="I5" s="5">
         <v>10</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
         <v>4000</v>
       </c>
-      <c r="K5" s="5">
+      <c r="L5" s="5">
         <v>5</v>
       </c>
-      <c r="L5" s="5">
+      <c r="M5" s="5">
         <v>7</v>
       </c>
-      <c r="M5" s="5">
+      <c r="N5" s="5">
         <v>500</v>
       </c>
-      <c r="N5" s="5">
+      <c r="O5" s="5">
         <v>7000</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="P5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="Q5" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1026,37 +1050,40 @@
       <c r="E6" s="5">
         <v>3000</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="5">
+        <v>100</v>
+      </c>
+      <c r="G6" s="12">
         <v>7</v>
       </c>
-      <c r="G6" s="12">
+      <c r="H6" s="12">
         <v>50</v>
       </c>
-      <c r="H6" s="5">
+      <c r="I6" s="5">
         <v>15</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>3</v>
       </c>
-      <c r="J6" s="5">
+      <c r="K6" s="5">
         <v>20000</v>
       </c>
-      <c r="K6" s="5">
+      <c r="L6" s="5">
         <v>1</v>
       </c>
-      <c r="L6" s="5">
+      <c r="M6" s="5">
         <v>6</v>
       </c>
-      <c r="M6" s="5">
+      <c r="N6" s="5">
         <v>800</v>
       </c>
-      <c r="N6" s="5">
+      <c r="O6" s="5">
         <v>7000</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="P6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="Q6" s="5" t="s">
         <v>25</v>
       </c>
     </row>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1CF48A-79A5-41AE-AE1D-AF6DBA1DCB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72961559-D449-4F41-A958-E26FA1A33385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14790" yWindow="3780" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13410" yWindow="4650" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -945,7 +945,7 @@
         <v>300</v>
       </c>
       <c r="F4" s="5">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G4" s="12">
         <v>1</v>
@@ -998,7 +998,7 @@
         <v>2400</v>
       </c>
       <c r="F5" s="5">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G5" s="12">
         <v>3</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72961559-D449-4F41-A958-E26FA1A33385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A70FB8-BF2F-4879-81B9-AD9B84B8926C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13410" yWindow="4650" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -291,10 +291,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>生产时间（毫秒）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -324,6 +320,10 @@
   </si>
   <si>
     <t>自动回血万分比</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产时间（帧数，每秒20帧）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -780,13 +780,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>13</v>
@@ -886,13 +886,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>14</v>
@@ -919,7 +919,7 @@
         <v>16</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="P3" s="4" t="s">
         <v>20</v>
@@ -939,7 +939,7 @@
         <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="5">
         <v>300</v>
@@ -972,7 +972,7 @@
         <v>100</v>
       </c>
       <c r="O4" s="5">
-        <v>1800</v>
+        <v>20</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>28</v>
@@ -992,7 +992,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" s="5">
         <v>2400</v>
@@ -1025,7 +1025,7 @@
         <v>500</v>
       </c>
       <c r="O5" s="5">
-        <v>7000</v>
+        <v>140</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>22</v>
@@ -1045,7 +1045,7 @@
         <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" s="5">
         <v>3000</v>
@@ -1078,7 +1078,7 @@
         <v>800</v>
       </c>
       <c r="O6" s="5">
-        <v>7000</v>
+        <v>140</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>21</v>
@@ -1284,7 +1284,7 @@
         <v>57</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A70FB8-BF2F-4879-81B9-AD9B84B8926C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D287753-FE0F-44EB-BDD9-3BC832438C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13410" yWindow="4650" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4230" yWindow="3810" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="76">
   <si>
     <t>ID</t>
   </si>
@@ -166,10 +166,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>移动速度</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>BadgerTank</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -324,6 +320,29 @@
   </si>
   <si>
     <t>生产时间（帧数，每秒20帧）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Radius</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度
+10000=1米/秒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>半径
+10000=1米</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scale</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩放比例
+10000=1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -438,7 +457,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -449,16 +468,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -472,14 +485,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -748,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -762,89 +778,97 @@
     <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="13" max="13" width="11.25" customWidth="1"/>
+    <col min="14" max="14" width="12.375" customWidth="1"/>
+    <col min="15" max="15" width="15.125" customWidth="1"/>
+    <col min="16" max="16" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -853,82 +877,94 @@
       <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="K2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:19" ht="60" x14ac:dyDescent="0.15">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="P3" s="4" t="s">
+      <c r="R3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="S3" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -939,49 +975,55 @@
         <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="5">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4">
         <v>300</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>100</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="9">
         <v>1</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="9">
         <v>10</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>10</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>1</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>4000</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <v>1</v>
       </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-      <c r="N4" s="5">
+      <c r="M4" s="4">
+        <v>10000</v>
+      </c>
+      <c r="N4" s="4">
+        <v>10000</v>
+      </c>
+      <c r="O4" s="4">
+        <v>30000</v>
+      </c>
+      <c r="P4" s="4">
         <v>100</v>
       </c>
-      <c r="O4" s="5">
+      <c r="Q4" s="4">
         <v>20</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="R4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="S4" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -989,52 +1031,58 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="5">
+        <v>65</v>
+      </c>
+      <c r="E5" s="4">
         <v>2400</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>100</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="9">
         <v>3</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="9">
         <v>20</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <v>10</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>2</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
         <v>4000</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="4">
         <v>5</v>
       </c>
-      <c r="M5" s="5">
-        <v>7</v>
-      </c>
-      <c r="N5" s="5">
-        <v>500</v>
-      </c>
-      <c r="O5" s="5">
-        <v>140</v>
-      </c>
-      <c r="P5" s="5" t="s">
+      <c r="M5" s="4">
+        <v>10000</v>
+      </c>
+      <c r="N5" s="4">
+        <v>15000</v>
+      </c>
+      <c r="O5" s="4">
+        <v>60000</v>
+      </c>
+      <c r="P5" s="4">
+        <v>300</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>80</v>
+      </c>
+      <c r="R5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="S5" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1042,48 +1090,54 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="5">
+        <v>66</v>
+      </c>
+      <c r="E6" s="4">
         <v>3000</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>100</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="9">
         <v>7</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="9">
         <v>50</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
         <v>15</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>3</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="4">
         <v>20000</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="4">
         <v>1</v>
       </c>
-      <c r="M6" s="5">
-        <v>6</v>
-      </c>
-      <c r="N6" s="5">
-        <v>800</v>
-      </c>
-      <c r="O6" s="5">
-        <v>140</v>
-      </c>
-      <c r="P6" s="5" t="s">
+      <c r="M6" s="4">
+        <v>10000</v>
+      </c>
+      <c r="N6" s="4">
+        <v>20000</v>
+      </c>
+      <c r="O6" s="4">
+        <v>50000</v>
+      </c>
+      <c r="P6" s="4">
+        <v>500</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>100</v>
+      </c>
+      <c r="R6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Q6" s="5" t="s">
+      <c r="S6" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1109,78 +1163,78 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="C1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>51</v>
+        <v>59</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="C2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.15">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="B3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>52</v>
+      <c r="G3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1190,7 +1244,7 @@
       <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>10</v>
       </c>
       <c r="D4" s="2">
@@ -1200,13 +1254,13 @@
         <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1216,7 +1270,7 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>10</v>
       </c>
       <c r="D5" s="2">
@@ -1226,13 +1280,13 @@
         <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
@@ -1242,7 +1296,7 @@
       <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>15</v>
       </c>
       <c r="D6" s="2">
@@ -1252,39 +1306,39 @@
         <v>200</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
+      <c r="A7" s="10">
         <v>4</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="10">
         <v>1</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="10">
         <v>10</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="10">
         <v>0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="10">
         <v>30</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D287753-FE0F-44EB-BDD9-3BC832438C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBC3C31-6F52-4375-AEFD-F55D28E71F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="3810" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="945" yWindow="3375" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="4">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="L4" s="4">
         <v>1</v>
@@ -1055,7 +1055,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="4">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="L5" s="4">
         <v>5</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>42</v>
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>43</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="10">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>43</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBC3C31-6F52-4375-AEFD-F55D28E71F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3506116E-8665-4499-9FC2-F9AADE11B954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="3375" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3506116E-8665-4499-9FC2-F9AADE11B954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE2957E-18DE-4891-B421-B44AE6DF5982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="84">
   <si>
     <t>ID</t>
   </si>
@@ -250,10 +250,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>机枪子弹</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>炮弹</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -343,6 +339,42 @@
   <si>
     <t>缩放比例
 10000=1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitDistance</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageRadius</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxDamageTargets</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShareDamage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中距离（万分比，5000=0.5米）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害半径（万分比，0=单体）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大伤害目标数（-1=无限制）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>均摊伤害（0=全额，1=均摊）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（獾式坦克）机枪子弹</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -798,13 +830,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>13</v>
@@ -825,10 +857,10 @@
         <v>31</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>32</v>
@@ -837,7 +869,7 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>19</v>
@@ -916,13 +948,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>14</v>
@@ -937,25 +969,25 @@
         <v>45</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L3" s="11" t="s">
         <v>27</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P3" s="11" t="s">
         <v>16</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R3" s="7" t="s">
         <v>20</v>
@@ -975,7 +1007,7 @@
         <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E4" s="4">
         <v>300</v>
@@ -1034,7 +1066,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="4">
         <v>2400</v>
@@ -1055,10 +1087,10 @@
         <v>2</v>
       </c>
       <c r="K5" s="4">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="L5" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M5" s="4">
         <v>10000</v>
@@ -1093,7 +1125,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" s="4">
         <v>3000</v>
@@ -1150,16 +1182,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DBC2DB-D077-4C22-AD9B-3F1912F98524}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="5" width="10.75" customWidth="1"/>
-    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.125" customWidth="1"/>
+    <col min="2" max="4" width="10.75" customWidth="1"/>
+    <col min="5" max="5" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.75" customWidth="1"/>
+    <col min="10" max="10" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,19 +1210,31 @@
         <v>38</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1199,19 +1248,31 @@
         <v>37</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" ht="60" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1225,19 +1286,31 @@
         <v>39</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="K3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1251,19 +1324,31 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>25</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="K4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1277,19 +1362,31 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>30000</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
         <v>40</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>53</v>
+      <c r="K5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1303,19 +1400,31 @@
         <v>0</v>
       </c>
       <c r="E6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>200</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>54</v>
+      <c r="K6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>4</v>
       </c>
@@ -1328,17 +1437,29 @@
       <c r="D7" s="10">
         <v>0</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
         <v>50</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>67</v>
+      <c r="K7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE2957E-18DE-4891-B421-B44AE6DF5982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBA935D-BE2D-4D02-B7AE-AF4C94489A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -435,7 +435,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,6 +445,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,7 +495,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -528,6 +534,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -841,7 +856,7 @@
       <c r="G1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="13" t="s">
         <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -900,7 +915,7 @@
       <c r="G2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -959,7 +974,7 @@
       <c r="G3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="14" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -1018,7 +1033,7 @@
       <c r="G4" s="9">
         <v>1</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="15">
         <v>10</v>
       </c>
       <c r="I4" s="4">
@@ -1069,7 +1084,7 @@
         <v>64</v>
       </c>
       <c r="E5" s="4">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="F5" s="4">
         <v>100</v>
@@ -1077,7 +1092,7 @@
       <c r="G5" s="9">
         <v>3</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="15">
         <v>20</v>
       </c>
       <c r="I5" s="4">
@@ -1093,7 +1108,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="4">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="N5" s="4">
         <v>15000</v>
@@ -1136,8 +1151,8 @@
       <c r="G6" s="9">
         <v>7</v>
       </c>
-      <c r="H6" s="9">
-        <v>50</v>
+      <c r="H6" s="15">
+        <v>20</v>
       </c>
       <c r="I6" s="4">
         <v>15</v>
@@ -1336,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>42</v>
@@ -1368,13 +1383,13 @@
         <v>30000</v>
       </c>
       <c r="G5" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>43</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBA935D-BE2D-4D02-B7AE-AF4C94489A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E5BE0B-9C43-43B6-BA61-293B969F1BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -1468,7 +1468,7 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>55</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E5BE0B-9C43-43B6-BA61-293B969F1BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5503F969-4118-4E15-BE3F-29B40DA0F825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="30885" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="1575" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
     <sheet name="ConfProjectile" sheetId="2" r:id="rId2"/>
+    <sheet name="ConfRestraint" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
   <si>
     <t>ID</t>
   </si>
@@ -376,13 +377,49 @@
   <si>
     <t>（獾式坦克）机枪子弹</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>大兵</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>獾式坦克</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>灰熊坦克</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Infantry</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BadgerTank</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>GrizzlyTank</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,8 +471,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,6 +502,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -495,7 +552,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -543,6 +600,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1025,7 +1097,7 @@
         <v>63</v>
       </c>
       <c r="E4" s="4">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F4" s="4">
         <v>100</v>
@@ -1034,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I4" s="4">
         <v>10</v>
@@ -1043,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="L4" s="4">
         <v>1</v>
@@ -1084,7 +1156,7 @@
         <v>64</v>
       </c>
       <c r="E5" s="4">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="F5" s="4">
         <v>100</v>
@@ -1093,7 +1165,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I5" s="4">
         <v>10</v>
@@ -1102,7 +1174,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="4">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="L5" s="4">
         <v>1</v>
@@ -1120,7 +1192,7 @@
         <v>300</v>
       </c>
       <c r="Q5" s="4">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>22</v>
@@ -1143,7 +1215,7 @@
         <v>65</v>
       </c>
       <c r="E6" s="4">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="F6" s="4">
         <v>100</v>
@@ -1152,7 +1224,7 @@
         <v>7</v>
       </c>
       <c r="H6" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I6" s="4">
         <v>15</v>
@@ -1161,7 +1233,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="4">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="L6" s="4">
         <v>1</v>
@@ -1179,7 +1251,7 @@
         <v>500</v>
       </c>
       <c r="Q6" s="4">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>21</v>
@@ -1351,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>42</v>
@@ -1389,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>43</v>
@@ -1427,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>41</v>
@@ -1481,4 +1553,122 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5815676E-82BE-4DAD-8351-2F2C0D1B67AF}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.15">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.15">
+      <c r="A2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.15">
+      <c r="A3" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="16">
+        <v>1</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="16">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="16">
+        <v>4000</v>
+      </c>
+      <c r="E4" s="16">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="16">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="16">
+        <v>20000</v>
+      </c>
+      <c r="D5" s="16">
+        <v>10000</v>
+      </c>
+      <c r="E5" s="16">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="16">
+        <v>3</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="16">
+        <v>9000</v>
+      </c>
+      <c r="D6" s="16">
+        <v>15000</v>
+      </c>
+      <c r="E6" s="16">
+        <v>10000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5503F969-4118-4E15-BE3F-29B40DA0F825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74C72C3-E6D0-4746-8E2E-D532B82DEB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="960" yWindow="1575" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="95">
   <si>
     <t>ID</t>
   </si>
@@ -413,6 +413,14 @@
   <si>
     <t>string</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>WarningRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>预警范围</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -552,7 +560,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -614,6 +622,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -883,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="13.125" customWidth="1"/>
@@ -893,20 +907,21 @@
     <col min="6" max="6" width="10.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.25" customWidth="1"/>
     <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.25" customWidth="1"/>
-    <col min="14" max="14" width="12.375" customWidth="1"/>
-    <col min="15" max="15" width="15.125" customWidth="1"/>
-    <col min="16" max="16" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="44.625" customWidth="1"/>
+    <col min="9" max="9" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.25" customWidth="1"/>
+    <col min="15" max="15" width="12.375" customWidth="1"/>
+    <col min="16" max="16" width="15.125" customWidth="1"/>
+    <col min="17" max="17" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -931,41 +946,44 @@
       <c r="H1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -990,41 +1008,44 @@
       <c r="H2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="21" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="60" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:20" ht="60" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1049,41 +1070,44 @@
       <c r="H3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="Q3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1108,41 +1132,44 @@
       <c r="H4" s="15">
         <v>0</v>
       </c>
-      <c r="I4" s="4">
-        <v>10</v>
+      <c r="I4" s="15">
+        <v>20</v>
       </c>
       <c r="J4" s="4">
+        <v>12</v>
+      </c>
+      <c r="K4" s="4">
         <v>1</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
         <v>10000</v>
       </c>
-      <c r="L4" s="4">
+      <c r="M4" s="4">
         <v>1</v>
-      </c>
-      <c r="M4" s="4">
-        <v>10000</v>
       </c>
       <c r="N4" s="4">
         <v>10000</v>
       </c>
       <c r="O4" s="4">
+        <v>10000</v>
+      </c>
+      <c r="P4" s="4">
         <v>30000</v>
       </c>
-      <c r="P4" s="4">
+      <c r="Q4" s="4">
         <v>100</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="R4" s="4">
         <v>20</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="S4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1167,41 +1194,44 @@
       <c r="H5" s="15">
         <v>0</v>
       </c>
-      <c r="I5" s="4">
-        <v>10</v>
+      <c r="I5" s="15">
+        <v>20</v>
       </c>
       <c r="J5" s="4">
+        <v>20</v>
+      </c>
+      <c r="K5" s="4">
         <v>2</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <v>12000</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <v>1</v>
       </c>
-      <c r="M5" s="4">
+      <c r="N5" s="4">
         <v>8000</v>
       </c>
-      <c r="N5" s="4">
+      <c r="O5" s="4">
         <v>15000</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>60000</v>
       </c>
-      <c r="P5" s="4">
+      <c r="Q5" s="4">
         <v>300</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="R5" s="4">
         <v>50</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="S5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="T5" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1226,37 +1256,40 @@
       <c r="H6" s="15">
         <v>0</v>
       </c>
-      <c r="I6" s="4">
-        <v>15</v>
+      <c r="I6" s="15">
+        <v>20</v>
       </c>
       <c r="J6" s="4">
+        <v>24</v>
+      </c>
+      <c r="K6" s="4">
         <v>3</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="4">
         <v>15000</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
         <v>1</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="4">
         <v>10000</v>
       </c>
-      <c r="N6" s="4">
+      <c r="O6" s="4">
         <v>20000</v>
       </c>
-      <c r="O6" s="4">
+      <c r="P6" s="4">
         <v>50000</v>
       </c>
-      <c r="P6" s="4">
+      <c r="Q6" s="4">
         <v>500</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="R6" s="4">
         <v>80</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="S6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="S6" s="4" t="s">
+      <c r="T6" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1452,7 +1485,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="2">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="G5" s="2">
         <v>8</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74C72C3-E6D0-4746-8E2E-D532B82DEB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3FD143-B04F-43E5-9F23-3296E90986F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="960" yWindow="1575" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1133,10 +1133,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J4" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -1195,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K5" s="4">
         <v>2</v>
@@ -1257,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J6" s="4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K6" s="4">
         <v>3</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3FD143-B04F-43E5-9F23-3296E90986F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114E4878-3715-4D32-8215-36223423BBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="1575" windowWidth="30885" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="915" yWindow="4125" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -116,35 +116,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>灰熊坦克</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>獾式坦克</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>范围攻击，适合快速消灭士兵</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>价格便宜，大量士兵可以快速歼灭灰熊坦克</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>价格高昂，攻击极高，适合攻击獾式坦克和建筑</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>AtkInterval</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>攻击目标数量</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>大兵</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -171,10 +151,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>GrizzlyTank</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>子弹类型
 1=子弹；
 2=炮弹；</t>
@@ -247,14 +223,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>步枪子弹</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>炮弹</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>音频</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -420,6 +388,46 @@
   </si>
   <si>
     <t>预警范围</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dog</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>反重装步兵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>重装坦克</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备高爆反装甲武器的轻步兵单位，专精对抗重型装甲目标。机动灵活、造价低廉，适合成群作战，能有效瘫痪或摧毁敌方重装坦克，但对轻型火力和范围攻击极为脆弱。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>高速轻型坦克，配备短程范围爆炸武器，可对密集步兵集群造成大面积杀伤。拥有优秀的机动性和射速，擅长清剿步兵和支援推进，但装甲薄弱，难以对抗中重型载具。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>装甲厚重、火力强大的主战坦克，主炮可精准击毁轻型载具。凭借坚固防护和稳定输出，在正面交锋中压制獾式坦克等轻型单位，但速度缓慢，易被大量反装甲步兵围攻。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>反重装步兵</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>重装坦克</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>重装坦克炮弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>反重装步兵子弹</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -482,6 +490,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -560,7 +569,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -629,6 +638,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -917,8 +938,8 @@
     <col min="16" max="16" width="15.125" customWidth="1"/>
     <col min="17" max="17" width="12.75" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="44.625" customWidth="1"/>
+    <col min="19" max="19" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="44.625" style="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15" x14ac:dyDescent="0.25">
@@ -932,13 +953,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>13</v>
@@ -947,39 +968,39 @@
         <v>11</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="23" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1041,7 +1062,7 @@
       <c r="S2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="24" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1050,19 +1071,19 @@
         <v>4</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>14</v>
@@ -1071,43 +1092,43 @@
         <v>12</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>16</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="S3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="T3" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="66" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1115,10 +1136,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E4" s="4">
         <v>120</v>
@@ -1162,14 +1183,14 @@
       <c r="R4" s="4">
         <v>20</v>
       </c>
-      <c r="S4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="S4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T4" s="25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="66" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1177,10 +1198,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4">
         <v>250</v>
@@ -1225,13 +1246,13 @@
         <v>50</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="T5" s="25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="66" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1239,10 +1260,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E6" s="4">
         <v>600</v>
@@ -1286,11 +1307,11 @@
       <c r="R6" s="4">
         <v>80</v>
       </c>
-      <c r="S6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>25</v>
+      <c r="S6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T6" s="25" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1324,34 +1345,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
@@ -1362,10 +1383,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>8</v>
@@ -1380,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>6</v>
@@ -1397,37 +1418,37 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -1459,13 +1480,13 @@
         <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -1497,13 +1518,13 @@
         <v>60</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -1535,13 +1556,13 @@
         <v>80</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -1573,13 +1594,13 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1593,6 +1614,7 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.625" customWidth="1"/>
     <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.875" bestFit="1" customWidth="1"/>
@@ -1603,16 +1625,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.15">
@@ -1620,16 +1642,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.15">
@@ -1637,16 +1659,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
@@ -1654,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C4" s="16">
         <v>10000</v>
@@ -1671,7 +1693,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C5" s="16">
         <v>20000</v>
@@ -1688,7 +1710,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C6" s="16">
         <v>9000</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114E4878-3715-4D32-8215-36223423BBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AC0FEA-6F4C-4A1C-BE57-D641B8F7F71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="4125" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10875" yWindow="3765" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -116,10 +116,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>獾式坦克</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>AtkInterval</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -135,19 +131,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Infantry</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>AtkCount</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Speed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BadgerTank</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -260,18 +248,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>images/Infantry</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>images/BadgerTank</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>images/GrizzlyTank</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>碉堡机枪子弹</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -391,10 +367,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>dog</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>反重装步兵</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -428,6 +400,33 @@
   </si>
   <si>
     <t>反重装步兵子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AntiUnit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeavyTank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightTank</t>
+  </si>
+  <si>
+    <t>images/AntiUnit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/LightTank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/HeavyTank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>獾式战车</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -953,13 +952,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>13</v>
@@ -968,34 +967,34 @@
         <v>11</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>19</v>
@@ -1071,19 +1070,19 @@
         <v>4</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>14</v>
@@ -1092,34 +1091,34 @@
         <v>12</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>16</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="S3" s="7" t="s">
         <v>20</v>
@@ -1136,10 +1135,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E4" s="4">
         <v>120</v>
@@ -1169,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="O4" s="4">
         <v>10000</v>
@@ -1184,10 +1183,10 @@
         <v>20</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="T4" s="25" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="66" x14ac:dyDescent="0.3">
@@ -1198,10 +1197,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="E5" s="4">
         <v>250</v>
@@ -1231,7 +1230,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="O5" s="4">
         <v>15000</v>
@@ -1245,11 +1244,11 @@
       <c r="R5" s="4">
         <v>50</v>
       </c>
-      <c r="S5" s="4" t="s">
-        <v>21</v>
+      <c r="S5" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="T5" s="25" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="66" x14ac:dyDescent="0.3">
@@ -1260,10 +1259,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="E6" s="4">
         <v>600</v>
@@ -1293,7 +1292,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="O6" s="4">
         <v>20000</v>
@@ -1308,10 +1307,10 @@
         <v>80</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1345,34 +1344,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
@@ -1383,10 +1382,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>8</v>
@@ -1401,7 +1400,7 @@
         <v>8</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>6</v>
@@ -1418,37 +1417,37 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -1480,13 +1479,13 @@
         <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -1518,13 +1517,13 @@
         <v>60</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -1556,13 +1555,13 @@
         <v>80</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -1594,13 +1593,13 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1625,16 +1624,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>82</v>
-      </c>
       <c r="E1" s="18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.15">
@@ -1642,16 +1641,16 @@
         <v>8</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.15">
@@ -1659,16 +1658,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
@@ -1676,7 +1675,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C4" s="16">
         <v>10000</v>
@@ -1693,7 +1692,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C5" s="16">
         <v>20000</v>
@@ -1710,7 +1709,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C6" s="16">
         <v>9000</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AC0FEA-6F4C-4A1C-BE57-D641B8F7F71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE2E13B-CD24-431A-B5C5-8DF01B0970CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10875" yWindow="3765" windowWidth="34560" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11370" yWindow="3060" windowWidth="34560" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="98">
   <si>
     <t>ID</t>
   </si>
@@ -165,15 +165,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Shell</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Bullet</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cartridge</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -282,11 +274,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>缩放比例
-10000=1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>HitDistance</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -427,6 +414,23 @@
   </si>
   <si>
     <t>獾式战车</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩放比例万分比
+(10000=1)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -952,13 +956,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>13</v>
@@ -967,13 +971,13 @@
         <v>11</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>21</v>
@@ -982,10 +986,10 @@
         <v>24</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>25</v>
@@ -994,7 +998,7 @@
         <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>19</v>
@@ -1076,13 +1080,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>14</v>
@@ -1091,34 +1095,34 @@
         <v>12</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>22</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>16</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S3" s="7" t="s">
         <v>20</v>
@@ -1135,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="E4" s="4">
         <v>120</v>
@@ -1183,10 +1187,10 @@
         <v>20</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T4" s="25" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="66" x14ac:dyDescent="0.3">
@@ -1197,10 +1201,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E5" s="4">
         <v>250</v>
@@ -1245,10 +1249,10 @@
         <v>50</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="T5" s="25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="66" x14ac:dyDescent="0.3">
@@ -1259,10 +1263,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E6" s="4">
         <v>600</v>
@@ -1307,10 +1311,10 @@
         <v>80</v>
       </c>
       <c r="S6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="T6" s="25" t="s">
         <v>82</v>
-      </c>
-      <c r="T6" s="25" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1322,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92DBC2DB-D077-4C22-AD9B-3F1912F98524}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="4" width="10.75" customWidth="1"/>
@@ -1332,11 +1336,12 @@
     <col min="8" max="8" width="15.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.75" customWidth="1"/>
     <col min="10" max="10" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.125" customWidth="1"/>
+    <col min="11" max="11" width="11.875" customWidth="1"/>
+    <col min="12" max="12" width="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1350,31 +1355,34 @@
         <v>29</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>64</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1406,13 +1414,16 @@
         <v>6</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="60" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1420,22 +1431,22 @@
         <v>26</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>31</v>
@@ -1443,14 +1454,17 @@
       <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K3" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1479,16 +1493,19 @@
         <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>46</v>
+        <v>94</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5000</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1517,16 +1534,19 @@
         <v>60</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>44</v>
+        <v>95</v>
+      </c>
+      <c r="K5" s="2">
+        <v>20000</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1555,16 +1575,19 @@
         <v>80</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>45</v>
+        <v>96</v>
+      </c>
+      <c r="K6" s="2">
+        <v>20000</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>4</v>
       </c>
@@ -1593,13 +1616,16 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
+      </c>
+      <c r="K7" s="2">
+        <v>5000</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1624,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.15">
@@ -1641,7 +1667,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>3</v>
@@ -1658,16 +1684,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="20" t="s">
         <v>71</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
@@ -1675,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C4" s="16">
         <v>10000</v>
@@ -1692,7 +1718,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C5" s="16">
         <v>20000</v>
@@ -1709,7 +1735,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C6" s="16">
         <v>9000</v>

--- a/config/excel/Unit.xlsx
+++ b/config/excel/Unit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyZiegler\github\ra2\config\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE2E13B-CD24-431A-B5C5-8DF01B0970CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AF8944-CA4B-4500-97E6-5339CE2324E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11370" yWindow="3060" windowWidth="34560" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7890" yWindow="1935" windowWidth="34560" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConfUnit" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -162,10 +162,6 @@
   </si>
   <si>
     <t>伤害</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bullet</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -956,13 +952,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>13</v>
@@ -971,13 +967,13 @@
         <v>11</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>21</v>
@@ -986,10 +982,10 @@
         <v>24</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>25</v>
@@ -998,7 +994,7 @@
         <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>19</v>
@@ -1080,13 +1076,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>14</v>
@@ -1095,34 +1091,34 @@
         <v>12</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>22</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>16</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S3" s="7" t="s">
         <v>20</v>
@@ -1139,10 +1135,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4" s="4">
         <v>120</v>
@@ -1187,10 +1183,10 @@
         <v>20</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T4" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="66" x14ac:dyDescent="0.3">
@@ -1201,10 +1197,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E5" s="4">
         <v>250</v>
@@ -1249,10 +1245,10 @@
         <v>50</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T5" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="66" x14ac:dyDescent="0.3">
@@ -1263,10 +1259,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" s="4">
         <v>600</v>
@@ -1311,10 +1307,10 @@
         <v>80</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1355,31 +1351,31 @@
         <v>29</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
@@ -1431,22 +1427,22 @@
         <v>26</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>31</v>
@@ -1455,13 +1451,13 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
@@ -1493,16 +1489,16 @@
         <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K4" s="2">
         <v>5000</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
@@ -1534,16 +1530,16 @@
         <v>60</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K5" s="2">
         <v>20000</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
@@ -1575,16 +1571,16 @@
         <v>80</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K6" s="2">
         <v>20000</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
@@ -1604,10 +1600,10 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="10">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="G7" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -1616,16 +1612,16 @@
         <v>50</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="K7" s="2">
         <v>5000</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1650,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>73</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.15">
@@ -1667,7 +1663,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>3</v>
@@ -1684,16 +1680,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="D3" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="E3" s="20" t="s">
         <v>70</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
@@ -1701,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="16">
         <v>10000</v>
@@ -1718,7 +1714,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="16">
         <v>20000</v>
@@ -1735,7 +1731,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="16">
         <v>9000</v>
